--- a/Wind Power.xlsx
+++ b/Wind Power.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/electricity application/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Campus-Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3CBFD2-5FD0-AB4B-A1BA-F9DECC022EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A0D178-1ACB-AF40-9951-1EF20A749D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="113">
   <si>
     <t>Metrics</t>
   </si>
@@ -373,6 +373,12 @@
   </si>
   <si>
     <t>Production</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Spatial requirement</t>
   </si>
 </sst>
 </file>
@@ -11553,7 +11559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02F4A57-A2BE-384A-8025-E4A1F08C861C}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
@@ -11980,6 +11986,35 @@
       </c>
       <c r="I14">
         <v>0.89775450085911801</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15">
+        <v>1521</v>
+      </c>
+      <c r="C15">
+        <v>5281</v>
+      </c>
+      <c r="D15">
+        <v>3959</v>
+      </c>
+      <c r="E15">
+        <v>6362</v>
+      </c>
+      <c r="F15">
+        <v>5281</v>
+      </c>
+      <c r="G15">
+        <v>2124</v>
+      </c>
+      <c r="H15">
+        <v>11310</v>
+      </c>
+      <c r="I15">
+        <v>12868</v>
       </c>
     </row>
   </sheetData>
@@ -14413,7 +14448,7 @@
         <v>246272</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D84" s="12" t="s">
         <v>53</v>
       </c>
@@ -14421,7 +14456,7 @@
       <c r="F84" s="12"/>
       <c r="G84" s="12"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>77</v>
       </c>
@@ -14446,8 +14481,11 @@
       <c r="L85" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="N85" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
         <f t="shared" ref="A86:A93" si="0">$C$117*B86/1000</f>
         <v>726928.47499999998</v>
@@ -14483,7 +14521,7 @@
         <v>12502.717878087578</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
         <f t="shared" si="0"/>
         <v>1637586.125</v>
@@ -14519,7 +14557,7 @@
         <v>28165.463351735754</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88">
         <f t="shared" si="0"/>
         <v>1845279.9750000001</v>
@@ -14555,7 +14593,7 @@
         <v>31737.668459760775</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89">
         <f t="shared" si="0"/>
         <v>2396467.5</v>
@@ -14591,7 +14629,7 @@
         <v>41217.751246442567</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
         <f t="shared" si="0"/>
         <v>1318057.125</v>
@@ -14627,7 +14665,7 @@
         <v>22669.763185543412</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
         <f t="shared" si="0"/>
         <v>678999.125</v>
@@ -14663,7 +14701,7 @@
         <v>11678.362853158727</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <f t="shared" si="0"/>
         <v>2875761</v>
@@ -14699,7 +14737,7 @@
         <v>49461.301495731081</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <f t="shared" si="0"/>
         <v>3594701.25</v>
@@ -14735,7 +14773,7 @@
         <v>61826.626869663851</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="L96" t="s">
         <v>79</v>
       </c>
